--- a/Helldivers/Super Credits Log.xlsx
+++ b/Helldivers/Super Credits Log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\python_projects\Helldivers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D7D6EA-0296-472D-8CB8-81E3C4D11CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9379C1F-D40B-499F-B727-4F209BBC85EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{3980E34F-3276-48B4-AAA9-72DB210AB7A4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="53">
   <si>
     <t>Mission Time</t>
   </si>
@@ -168,6 +168,36 @@
   </si>
   <si>
     <t>Incorrect time</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Rapid Acquisition</t>
+  </si>
+  <si>
+    <t>Martale</t>
+  </si>
+  <si>
+    <t>Predator Strain</t>
+  </si>
+  <si>
+    <t>Gar Haren</t>
+  </si>
+  <si>
+    <t>Launch ICBM</t>
+  </si>
+  <si>
+    <t>Purge Hatcheries</t>
+  </si>
+  <si>
+    <t>Dysnc dupe</t>
+  </si>
+  <si>
+    <t>Rupture Strain</t>
+  </si>
+  <si>
+    <t>Brilliance</t>
   </si>
 </sst>
 </file>
@@ -209,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -220,6 +250,7 @@
     <xf numFmtId="45" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1850,7 +1881,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>46250</v>
       </c>
@@ -1891,82 +1922,557 @@
         <v>480</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C39" s="1"/>
-      <c r="F39" s="3"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C40" s="1"/>
-      <c r="F40" s="3"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C41" s="1"/>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C42" s="1"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C43" s="1"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C44" s="1"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C45" s="1"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="C46" s="1"/>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34">
+        <v>10</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F34" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L34" s="1">
+        <v>17</v>
+      </c>
+      <c r="M34">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35">
+        <v>10</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L35" s="1">
+        <v>18</v>
+      </c>
+      <c r="M35">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36">
+        <v>10</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="3">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="G36" s="1">
+        <v>0</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L36" s="1">
+        <v>19</v>
+      </c>
+      <c r="M36">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37">
+        <v>10</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="3">
+        <v>2.1608796296296296E-2</v>
+      </c>
+      <c r="G37" s="1">
+        <v>20</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L37" s="1">
+        <v>19</v>
+      </c>
+      <c r="M37">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38">
+        <v>10</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38" s="3">
+        <v>2.2256944444444444E-2</v>
+      </c>
+      <c r="G38" s="1">
+        <v>10</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L38" s="1">
+        <v>19</v>
+      </c>
+      <c r="M38">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39">
+        <v>10</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F39" s="3">
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L39" s="1">
+        <v>20</v>
+      </c>
+      <c r="M39">
+        <v>510</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D40">
+        <v>10</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G40" s="1">
+        <v>10</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L40" s="1">
+        <v>20</v>
+      </c>
+      <c r="M40">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41">
+        <v>10</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F41" s="3">
+        <v>2.6388888888888889E-2</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L41" s="1">
+        <v>20</v>
+      </c>
+      <c r="M41">
+        <v>520</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D42">
+        <v>10</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F42" s="3">
+        <v>1.3518518518518518E-2</v>
+      </c>
+      <c r="G42" s="1">
+        <v>20</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L42" s="1">
+        <v>20</v>
+      </c>
+      <c r="M42">
+        <v>540</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A43" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43">
+        <v>10</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1.8749999999999999E-2</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L43" s="1">
+        <v>21</v>
+      </c>
+      <c r="M43">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D44">
+        <v>10</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F44" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L44" s="1">
+        <v>22</v>
+      </c>
+      <c r="M44">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A45" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45">
+        <v>10</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L45" s="1">
+        <v>22</v>
+      </c>
+      <c r="M45">
+        <v>540</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46">
+        <v>10</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F46" s="3">
+        <v>1.5752314814814816E-2</v>
+      </c>
+      <c r="G46" s="1">
+        <v>30</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L46" s="1">
+        <v>22</v>
+      </c>
+      <c r="M46">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C47" s="1"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C48" s="1"/>
+      <c r="F48" s="4"/>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C49" s="1"/>
@@ -2007,9 +2513,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Terminid;Automatons; Illuminates" sqref="B2:B37" xr:uid="{D798BB62-A9AA-484F-B0C1-2284059A6DE0}">
-      <formula1>"Terminids, Automatons, lluminate"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I18" xr:uid="{8401F6A8-3ACC-45FE-A6B4-ABFE7E6BEC32}">
       <formula1>"No, Yes"</formula1>
     </dataValidation>
@@ -2019,22 +2522,25 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C18 C60" xr:uid="{CBAA832B-00A1-4E19-BB8D-1F53FBB66E4C}">
       <formula1>"N/A, Incineration Corps, Cyborgs, Predator Strain, Rupture Strain, Spore Burst Strain, Mindless Masses, Appropriators"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D40" xr:uid="{628F7E99-C793-498B-BB51-F86A87D5EBDA}">
-      <formula1>"10, 9, 8, 7, 6, 5, 4, 3, 2, 1"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1" xr:uid="{5FCC0AFB-2BD9-4418-A011-81BD0E0B864E}">
       <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production, Eradicate, Sabotage Supply Bases"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E20 E58:E59" xr:uid="{A02F080F-565E-4CBB-9F20-052DA9D7E4CF}">
       <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production, Eradicate, Sabotage Supply Bases, Take Down Overship"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21:E25 E57" xr:uid="{FED4EEA0-1D74-4EBF-A9E3-D929FD86EF61}">
+      <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production, Eradicate, Sabotage Supply Bases, Take Down Overship, Repel Invasion"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Terminid;Automatons; Illuminates" sqref="B2:B46" xr:uid="{D798BB62-A9AA-484F-B0C1-2284059A6DE0}">
+      <formula1>"Terminids, Automatons, lluminate"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D38 D40:D42" xr:uid="{628F7E99-C793-498B-BB51-F86A87D5EBDA}">
+      <formula1>"10, 9, 8, 7, 6, 5, 4, 3, 2, 1"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C19:C59" xr:uid="{CD443ED4-E4BF-4C51-99FC-0D0F9FA657AD}">
       <formula1>"N/A, Incineration Corps, Cyborgs, Predator Strain, Rupture Strain, Spore Burst Strain, Mindless Masses, Appropriators,Vote Snatchers"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21:E25 E57" xr:uid="{FED4EEA0-1D74-4EBF-A9E3-D929FD86EF61}">
-      <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production, Eradicate, Sabotage Supply Bases, Take Down Overship, Repel Invasion"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E26:E56" xr:uid="{7C4AB8FE-A995-45E4-A1F6-5AB74AD7C797}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E26:E38 E40:E56" xr:uid="{7C4AB8FE-A995-45E4-A1F6-5AB74AD7C797}">
       <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production, Eradicate, Sabotage Supply Bases, Take Down Overship, Repel Invasion"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Helldivers/Super Credits Log.xlsx
+++ b/Helldivers/Super Credits Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\python_projects\Helldivers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9379C1F-D40B-499F-B727-4F209BBC85EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82BCE1D-C633-4530-A17F-F063D91D1846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{3980E34F-3276-48B4-AAA9-72DB210AB7A4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="59">
   <si>
     <t>Mission Time</t>
   </si>
@@ -198,6 +198,24 @@
   </si>
   <si>
     <t>Brilliance</t>
+  </si>
+  <si>
+    <t>Zefia</t>
+  </si>
+  <si>
+    <t>Crash Dupe</t>
+  </si>
+  <si>
+    <t>Incorrect mission type and time</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Sabotage Orgo-Plasma Synthesis</t>
+  </si>
+  <si>
+    <t>Annex Untapped Mineral Sites</t>
   </si>
 </sst>
 </file>
@@ -239,7 +257,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -250,7 +268,10 @@
     <xf numFmtId="45" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -601,7 +622,7 @@
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.1796875" customWidth="1"/>
-    <col min="14" max="14" width="19.81640625" customWidth="1"/>
+    <col min="14" max="14" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
@@ -685,6 +706,9 @@
       <c r="L2" s="1">
         <v>1</v>
       </c>
+      <c r="M2" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
@@ -723,6 +747,9 @@
       <c r="L3" s="1">
         <v>1</v>
       </c>
+      <c r="M3" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="N3" s="1" t="s">
         <v>42</v>
       </c>
@@ -764,6 +791,9 @@
       <c r="L4" s="1">
         <v>1</v>
       </c>
+      <c r="M4" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="N4" s="1" t="s">
         <v>42</v>
       </c>
@@ -805,6 +835,9 @@
       <c r="L5" s="1">
         <v>2</v>
       </c>
+      <c r="M5" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="N5" s="1" t="s">
         <v>42</v>
       </c>
@@ -846,6 +879,9 @@
       <c r="L6" s="1">
         <v>3</v>
       </c>
+      <c r="M6" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="N6" s="1" t="s">
         <v>42</v>
       </c>
@@ -887,6 +923,9 @@
       <c r="L7" s="1">
         <v>4</v>
       </c>
+      <c r="M7" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
@@ -925,6 +964,9 @@
       <c r="L8" s="1">
         <v>5</v>
       </c>
+      <c r="M8" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
@@ -963,6 +1005,9 @@
       <c r="L9" s="1">
         <v>5</v>
       </c>
+      <c r="M9" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
@@ -1001,6 +1046,9 @@
       <c r="L10" s="1">
         <v>6</v>
       </c>
+      <c r="M10" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
@@ -1039,6 +1087,9 @@
       <c r="L11" s="1">
         <v>7</v>
       </c>
+      <c r="M11" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
@@ -1077,6 +1128,9 @@
       <c r="L12" s="1">
         <v>8</v>
       </c>
+      <c r="M12" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
@@ -1115,6 +1169,9 @@
       <c r="L13" s="1">
         <v>9</v>
       </c>
+      <c r="M13" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
@@ -1153,6 +1210,9 @@
       <c r="L14" s="1">
         <v>9</v>
       </c>
+      <c r="M14" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
@@ -1191,6 +1251,9 @@
       <c r="L15" s="1">
         <v>9</v>
       </c>
+      <c r="M15" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
@@ -1229,6 +1292,9 @@
       <c r="L16" s="1">
         <v>10</v>
       </c>
+      <c r="M16" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="N16" s="1"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
@@ -1268,6 +1334,9 @@
       <c r="L17" s="1">
         <v>10</v>
       </c>
+      <c r="M17" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
@@ -1306,6 +1375,9 @@
       <c r="L18" s="1">
         <v>10</v>
       </c>
+      <c r="M18" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
@@ -1344,6 +1416,9 @@
       <c r="L19" s="1">
         <v>11</v>
       </c>
+      <c r="M19" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
@@ -1382,6 +1457,9 @@
       <c r="L20" s="1">
         <v>11</v>
       </c>
+      <c r="M20" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="N20" s="1" t="s">
         <v>42</v>
       </c>
@@ -1423,6 +1501,9 @@
       <c r="L21" s="1">
         <v>12</v>
       </c>
+      <c r="M21" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="N21" s="1" t="s">
         <v>42</v>
       </c>
@@ -1464,6 +1545,9 @@
       <c r="L22" s="1">
         <v>13</v>
       </c>
+      <c r="M22" s="5" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
@@ -2468,46 +2552,285 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C47" s="1"/>
+      <c r="A47" s="4">
+        <v>46266</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D47">
+        <v>10</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F47" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L47" s="1">
+        <v>23</v>
+      </c>
+      <c r="M47">
+        <v>570</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C48" s="1"/>
-      <c r="F48" s="4"/>
-    </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C49" s="1"/>
-    </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C50" s="1"/>
-    </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C51" s="1"/>
-    </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C52" s="1"/>
-    </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="4">
+        <v>46266</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48">
+        <v>10</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F48" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L48" s="1">
+        <v>24</v>
+      </c>
+      <c r="M48">
+        <v>570</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A49" s="4">
+        <v>46266</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49">
+        <v>10</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L49" s="1">
+        <v>24</v>
+      </c>
+      <c r="M49">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A50" s="4">
+        <v>46266</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50">
+        <v>10</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="3">
+        <v>2.2916666666666665E-2</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L50" s="1">
+        <v>24</v>
+      </c>
+      <c r="M50">
+        <v>570</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A51" s="4">
+        <v>46267</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51">
+        <v>10</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F51" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L51" s="1">
+        <v>25</v>
+      </c>
+      <c r="M51">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A52" s="4">
+        <v>46267</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52">
+        <v>10</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F52" s="3">
+        <v>2.2916666666666665E-2</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L52" s="1">
+        <v>25</v>
+      </c>
+      <c r="M52">
+        <v>570</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C53" s="1"/>
     </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C54" s="1"/>
     </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C55" s="1"/>
     </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C56" s="1"/>
     </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C57" s="1"/>
     </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C58" s="1"/>
     </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C59" s="1"/>
     </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C60" s="1"/>
     </row>
   </sheetData>
@@ -2537,11 +2860,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D38 D40:D42" xr:uid="{628F7E99-C793-498B-BB51-F86A87D5EBDA}">
       <formula1>"10, 9, 8, 7, 6, 5, 4, 3, 2, 1"</formula1>
     </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E26:E38 E40:E56" xr:uid="{7C4AB8FE-A995-45E4-A1F6-5AB74AD7C797}">
+      <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production, Eradicate, Sabotage Supply Bases, Take Down Overship, Repel Invasion"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C19:C59" xr:uid="{CD443ED4-E4BF-4C51-99FC-0D0F9FA657AD}">
       <formula1>"N/A, Incineration Corps, Cyborgs, Predator Strain, Rupture Strain, Spore Burst Strain, Mindless Masses, Appropriators,Vote Snatchers"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E26:E38 E40:E56" xr:uid="{7C4AB8FE-A995-45E4-A1F6-5AB74AD7C797}">
-      <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production, Eradicate, Sabotage Supply Bases, Take Down Overship, Repel Invasion"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Helldivers/Super Credits Log.xlsx
+++ b/Helldivers/Super Credits Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\python_projects\Helldivers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82BCE1D-C633-4530-A17F-F063D91D1846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF68804-A23B-4160-BB9B-A08129216500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{3980E34F-3276-48B4-AAA9-72DB210AB7A4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="62">
   <si>
     <t>Mission Time</t>
   </si>
@@ -216,6 +216,15 @@
   </si>
   <si>
     <t>Annex Untapped Mineral Sites</t>
+  </si>
+  <si>
+    <t>Trandor</t>
+  </si>
+  <si>
+    <t>Incineration Corps</t>
+  </si>
+  <si>
+    <t>Varylia</t>
   </si>
 </sst>
 </file>
@@ -2810,25 +2819,260 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C53" s="1"/>
+      <c r="A53" s="4">
+        <v>46282</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D53">
+        <v>10</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="3">
+        <v>4.8611111111111112E-3</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L53" s="1">
+        <v>26</v>
+      </c>
+      <c r="M53">
+        <v>570</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C54" s="1"/>
+      <c r="A54" s="4">
+        <v>46282</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D54">
+        <v>10</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F54" s="3">
+        <v>1.9976851851851853E-2</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L54" s="1">
+        <v>26</v>
+      </c>
+      <c r="M54">
+        <v>570</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C55" s="1"/>
+      <c r="A55" s="4">
+        <v>46282</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D55">
+        <v>10</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F55" s="3">
+        <v>2.7627314814814816E-2</v>
+      </c>
+      <c r="G55" s="1">
+        <v>10</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L55" s="1">
+        <v>26</v>
+      </c>
+      <c r="M55">
+        <v>580</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C56" s="1"/>
+      <c r="A56" s="4">
+        <v>46282</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D56">
+        <v>10</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F56" s="3">
+        <v>2.148148148148148E-2</v>
+      </c>
+      <c r="G56" s="1">
+        <v>40</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L56" s="1">
+        <v>27</v>
+      </c>
+      <c r="M56">
+        <v>620</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C57" s="1"/>
+      <c r="A57" s="4">
+        <v>46282</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D57">
+        <v>10</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="3">
+        <v>4.8611111111111112E-3</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L57" s="1">
+        <v>27</v>
+      </c>
+      <c r="M57">
+        <v>620</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C58" s="1"/>
+      <c r="A58" s="4">
+        <v>46282</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D58">
+        <v>10</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F58" s="3">
+        <v>2.148148148148148E-2</v>
+      </c>
+      <c r="G58" s="1">
+        <v>10</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L58" s="1">
+        <v>27</v>
+      </c>
+      <c r="M58">
+        <v>630</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C59" s="1"/>
+      <c r="F59" s="3"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C60" s="1"/>

--- a/Helldivers/Super Credits Log.xlsx
+++ b/Helldivers/Super Credits Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\python_projects\Helldivers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF68804-A23B-4160-BB9B-A08129216500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2D5E8B-89B2-40F1-9CB3-67317C8F7641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{3980E34F-3276-48B4-AAA9-72DB210AB7A4}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{3980E34F-3276-48B4-AAA9-72DB210AB7A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="69">
   <si>
     <t>Mission Time</t>
   </si>
@@ -225,13 +225,34 @@
   </si>
   <si>
     <t>Varylia</t>
+  </si>
+  <si>
+    <t>Incorrect time, super store item bought</t>
+  </si>
+  <si>
+    <t>Phact Bay</t>
+  </si>
+  <si>
+    <t>https://helldivers.wiki.gg/wiki/Missions</t>
+  </si>
+  <si>
+    <t>Zzaniah</t>
+  </si>
+  <si>
+    <t>Destroy Command Bunkers</t>
+  </si>
+  <si>
+    <t>Heeth</t>
+  </si>
+  <si>
+    <t>Received Supercredits from Warbond, Double check the rest info</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,6 +262,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -263,10 +292,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -281,8 +311,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -615,26 +648,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B874BC27-9F05-4CCB-84C0-24A63EA21ED1}">
-  <dimension ref="A1:N60"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O78"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.26953125" customWidth="1"/>
-    <col min="6" max="6" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.36328125" customWidth="1"/>
-    <col min="9" max="9" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="25.28515625" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" customWidth="1"/>
+    <col min="9" max="9" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.1796875" customWidth="1"/>
-    <col min="14" max="14" width="26" customWidth="1"/>
+    <col min="13" max="13" width="17.140625" customWidth="1"/>
+    <col min="14" max="14" width="38.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -677,8 +710,11 @@
       <c r="N1" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O1" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46218</v>
       </c>
@@ -718,8 +754,11 @@
       <c r="M2" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N2" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46218</v>
       </c>
@@ -763,7 +802,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>46218</v>
       </c>
@@ -807,7 +846,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>46218</v>
       </c>
@@ -851,7 +890,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>46219</v>
       </c>
@@ -895,7 +934,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>46219</v>
       </c>
@@ -935,8 +974,11 @@
       <c r="M7" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N7" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>46219</v>
       </c>
@@ -976,8 +1018,11 @@
       <c r="M8" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N8" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>46219</v>
       </c>
@@ -1017,8 +1062,11 @@
       <c r="M9" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N9" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>46219</v>
       </c>
@@ -1058,8 +1106,11 @@
       <c r="M10" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N10" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>46219</v>
       </c>
@@ -1099,8 +1150,11 @@
       <c r="M11" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N11" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>46220</v>
       </c>
@@ -1140,8 +1194,11 @@
       <c r="M12" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N12" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>46220</v>
       </c>
@@ -1181,8 +1238,11 @@
       <c r="M13" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N13" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>46220</v>
       </c>
@@ -1222,8 +1282,11 @@
       <c r="M14" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N14" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>46220</v>
       </c>
@@ -1263,8 +1326,11 @@
       <c r="M15" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N15" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>46246</v>
       </c>
@@ -1304,9 +1370,11 @@
       <c r="M16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N16" s="1"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N16" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>46246</v>
       </c>
@@ -1346,8 +1414,11 @@
       <c r="M17" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N17" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>46246</v>
       </c>
@@ -1387,8 +1458,11 @@
       <c r="M18" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N18" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>46246</v>
       </c>
@@ -1428,8 +1502,11 @@
       <c r="M19" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N19" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>46246</v>
       </c>
@@ -1473,7 +1550,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>46246</v>
       </c>
@@ -1517,7 +1594,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>46246</v>
       </c>
@@ -1557,8 +1634,11 @@
       <c r="M22" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N22" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>46246</v>
       </c>
@@ -1602,7 +1682,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>46246</v>
       </c>
@@ -1646,7 +1726,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>46249</v>
       </c>
@@ -1686,8 +1766,11 @@
       <c r="M25">
         <v>440</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N25" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>46249</v>
       </c>
@@ -1727,8 +1810,11 @@
       <c r="M26">
         <v>440</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N26" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>46249</v>
       </c>
@@ -1768,8 +1854,11 @@
       <c r="M27">
         <v>440</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N27" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>46249</v>
       </c>
@@ -1809,8 +1898,11 @@
       <c r="M28">
         <v>450</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N28" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>46249</v>
       </c>
@@ -1850,8 +1942,11 @@
       <c r="M29">
         <v>480</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N29" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>46250</v>
       </c>
@@ -1891,8 +1986,11 @@
       <c r="M30">
         <v>480</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N30" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>46250</v>
       </c>
@@ -1932,8 +2030,11 @@
       <c r="M31">
         <v>480</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N31" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>46250</v>
       </c>
@@ -1973,8 +2074,11 @@
       <c r="M32">
         <v>480</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N32" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>46250</v>
       </c>
@@ -2014,8 +2118,11 @@
       <c r="M33">
         <v>480</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N33" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>46257</v>
       </c>
@@ -2055,8 +2162,11 @@
       <c r="M34">
         <v>480</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N34" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>46257</v>
       </c>
@@ -2096,8 +2206,11 @@
       <c r="M35">
         <v>480</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N35" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>46257</v>
       </c>
@@ -2137,8 +2250,11 @@
       <c r="M36">
         <v>480</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N36" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>46257</v>
       </c>
@@ -2178,8 +2294,11 @@
       <c r="M37">
         <v>500</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N37" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>46257</v>
       </c>
@@ -2219,8 +2338,11 @@
       <c r="M38">
         <v>510</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N38" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>46259</v>
       </c>
@@ -2264,7 +2386,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>46259</v>
       </c>
@@ -2304,8 +2426,11 @@
       <c r="M40">
         <v>520</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N40" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>46259</v>
       </c>
@@ -2349,7 +2474,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>46260</v>
       </c>
@@ -2393,7 +2518,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>46260</v>
       </c>
@@ -2433,8 +2558,11 @@
       <c r="M43">
         <v>540</v>
       </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N43" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>46260</v>
       </c>
@@ -2474,8 +2602,11 @@
       <c r="M44">
         <v>540</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N44" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>46260</v>
       </c>
@@ -2519,7 +2650,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>46260</v>
       </c>
@@ -2559,8 +2690,11 @@
       <c r="M46">
         <v>570</v>
       </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N46" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>46266</v>
       </c>
@@ -2604,7 +2738,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>46266</v>
       </c>
@@ -2648,7 +2782,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>46266</v>
       </c>
@@ -2688,8 +2822,11 @@
       <c r="M49">
         <v>570</v>
       </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N49" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>46266</v>
       </c>
@@ -2733,7 +2870,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>46267</v>
       </c>
@@ -2773,8 +2910,11 @@
       <c r="M51">
         <v>570</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N51" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>46267</v>
       </c>
@@ -2818,7 +2958,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>46282</v>
       </c>
@@ -2862,7 +3002,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>46282</v>
       </c>
@@ -2902,8 +3042,11 @@
       <c r="M54">
         <v>570</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N54" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>46282</v>
       </c>
@@ -2943,8 +3086,11 @@
       <c r="M55">
         <v>580</v>
       </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N55" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>46282</v>
       </c>
@@ -2984,8 +3130,11 @@
       <c r="M56">
         <v>620</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N56" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>46282</v>
       </c>
@@ -3029,7 +3178,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>46282</v>
       </c>
@@ -3069,24 +3218,859 @@
       <c r="M58">
         <v>630</v>
       </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C59" s="1"/>
-      <c r="F59" s="3"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C60" s="1"/>
+      <c r="N58" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" s="4">
+        <v>46289</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D59">
+        <v>10</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="3">
+        <v>4.8611111111111112E-3</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L59" s="1">
+        <v>28</v>
+      </c>
+      <c r="M59">
+        <v>240</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" s="4">
+        <v>46289</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D60">
+        <v>10</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F60" s="3">
+        <v>1.7361111111111112E-2</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L60" s="1">
+        <v>28</v>
+      </c>
+      <c r="M60">
+        <v>240</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
+        <v>46289</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D61">
+        <v>10</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="3">
+        <v>1.7361111111111112E-2</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L61" s="1">
+        <v>28</v>
+      </c>
+      <c r="M61">
+        <v>240</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" s="4">
+        <v>46289</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D62">
+        <v>10</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F62" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L62" s="1">
+        <v>29</v>
+      </c>
+      <c r="M62">
+        <v>240</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="4">
+        <v>46289</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D63">
+        <v>10</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" s="3">
+        <v>3.6574074074074074E-3</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L63" s="1">
+        <v>29</v>
+      </c>
+      <c r="M63">
+        <v>240</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" s="4">
+        <v>46289</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D64">
+        <v>10</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F64" s="3">
+        <v>2.2372685185185186E-2</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L64" s="1">
+        <v>29</v>
+      </c>
+      <c r="M64">
+        <v>240</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" s="4">
+        <v>46289</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65">
+        <v>10</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F65" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L65" s="1">
+        <v>30</v>
+      </c>
+      <c r="M65">
+        <v>240</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" s="4">
+        <v>46289</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66">
+        <v>10</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" s="3">
+        <v>5.8449074074074072E-3</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L66" s="1">
+        <v>30</v>
+      </c>
+      <c r="M66">
+        <v>240</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" s="4">
+        <v>46289</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67">
+        <v>10</v>
+      </c>
+      <c r="E67" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" s="3">
+        <v>1.1689814814814814E-2</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L67" s="1">
+        <v>30</v>
+      </c>
+      <c r="M67">
+        <v>240</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" s="4">
+        <v>46289</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68">
+        <v>10</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" s="3">
+        <v>7.0486111111111114E-3</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L68" s="1">
+        <v>31</v>
+      </c>
+      <c r="M68">
+        <v>240</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" s="4">
+        <v>46289</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69">
+        <v>10</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F69" s="3">
+        <v>2.6979166666666665E-2</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L69" s="1">
+        <v>31</v>
+      </c>
+      <c r="M69">
+        <v>240</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" s="4">
+        <v>46289</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70">
+        <v>10</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70" s="3">
+        <v>2.5451388888888888E-2</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L70" s="1">
+        <v>31</v>
+      </c>
+      <c r="M70">
+        <v>240</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" s="4">
+        <v>46289</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71">
+        <v>10</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F71" s="3">
+        <v>2.6203703703703705E-2</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L71" s="1">
+        <v>32</v>
+      </c>
+      <c r="M71">
+        <v>240</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" s="4">
+        <v>46289</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72">
+        <v>10</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F72" s="3">
+        <v>5.1504629629629626E-3</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L72" s="1">
+        <v>32</v>
+      </c>
+      <c r="M72">
+        <v>240</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" s="4">
+        <v>46289</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73">
+        <v>10</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F73" s="3">
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L73" s="1">
+        <v>32</v>
+      </c>
+      <c r="M73">
+        <v>240</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" s="4">
+        <v>46293</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D74">
+        <v>10</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F74" s="3">
+        <v>1.7256944444444443E-2</v>
+      </c>
+      <c r="G74" s="1">
+        <v>20</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L74" s="1">
+        <v>33</v>
+      </c>
+      <c r="M74">
+        <v>260</v>
+      </c>
+      <c r="N74" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" s="4">
+        <v>46293</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D75">
+        <v>10</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F75" s="3">
+        <v>4.8611111111111112E-3</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L75" s="1">
+        <v>33</v>
+      </c>
+      <c r="M75">
+        <v>260</v>
+      </c>
+      <c r="N75" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" s="4">
+        <v>46293</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D76">
+        <v>10</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F76" s="3">
+        <v>2.732638888888889E-2</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L76" s="1">
+        <v>33</v>
+      </c>
+      <c r="M76">
+        <v>260</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" s="4">
+        <v>46304</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D77">
+        <v>10</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F77" s="3">
+        <v>1.7326388888888888E-2</v>
+      </c>
+      <c r="G77" s="1">
+        <v>20</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L77" s="1">
+        <v>33</v>
+      </c>
+      <c r="M77">
+        <v>380</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F78" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="10">
+  <dataValidations disablePrompts="1" count="10">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I18" xr:uid="{8401F6A8-3ACC-45FE-A6B4-ABFE7E6BEC32}">
       <formula1>"No, Yes"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:K18" xr:uid="{164DCC27-42E4-47D3-A8E6-BB0649B15D98}">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C18 C60" xr:uid="{CBAA832B-00A1-4E19-BB8D-1F53FBB66E4C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C18" xr:uid="{CBAA832B-00A1-4E19-BB8D-1F53FBB66E4C}">
       <formula1>"N/A, Incineration Corps, Cyborgs, Predator Strain, Rupture Strain, Spore Burst Strain, Mindless Masses, Appropriators"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1" xr:uid="{5FCC0AFB-2BD9-4418-A011-81BD0E0B864E}">
@@ -3107,11 +4091,14 @@
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E26:E38 E40:E56" xr:uid="{7C4AB8FE-A995-45E4-A1F6-5AB74AD7C797}">
       <formula1>"Spread Democracy, Retrieve Valuable Data, Emergency Evacuation, Launch ICBM, Conduct Geological Survey, Evacuate High-Value Assets, Blitz, Sabotage Air Base, Halt Cyborg Production, Eradicate, Sabotage Supply Bases, Take Down Overship, Repel Invasion"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C19:C59" xr:uid="{CD443ED4-E4BF-4C51-99FC-0D0F9FA657AD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C19:C73" xr:uid="{CD443ED4-E4BF-4C51-99FC-0D0F9FA657AD}">
       <formula1>"N/A, Incineration Corps, Cyborgs, Predator Strain, Rupture Strain, Spore Burst Strain, Mindless Masses, Appropriators,Vote Snatchers"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="O1" r:id="rId1" xr:uid="{020A9D89-FE87-4E0C-8F44-8F145C6D3407}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Helldivers/Super Credits Log.xlsx
+++ b/Helldivers/Super Credits Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\python_projects\Helldivers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2D5E8B-89B2-40F1-9CB3-67317C8F7641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857714E1-56B5-45C4-ADDF-78DC541366EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{3980E34F-3276-48B4-AAA9-72DB210AB7A4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="71">
   <si>
     <t>Mission Time</t>
   </si>
@@ -245,7 +245,13 @@
     <t>Heeth</t>
   </si>
   <si>
-    <t>Received Supercredits from Warbond, Double check the rest info</t>
+    <t>Received Supercredits from Warbond</t>
+  </si>
+  <si>
+    <t>Fauriant</t>
+  </si>
+  <si>
+    <t>Incorrect time, had too much fun</t>
   </si>
 </sst>
 </file>
@@ -296,7 +302,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -312,7 +318,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -648,11 +653,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B874BC27-9F05-4CCB-84C0-24A63EA21ED1}">
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.85546875" customWidth="1"/>
     <col min="5" max="5" width="25.28515625" customWidth="1"/>
@@ -4059,7 +4063,174 @@
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F78" s="7"/>
+      <c r="A78" s="4">
+        <v>46308</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D78">
+        <v>10</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F78" s="3">
+        <v>0.85972222222222228</v>
+      </c>
+      <c r="G78" s="1">
+        <v>20</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L78" s="1">
+        <v>34</v>
+      </c>
+      <c r="M78">
+        <v>500</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79" s="4">
+        <v>46308</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D79">
+        <v>10</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F79" s="3">
+        <v>1.8379629629629631E-2</v>
+      </c>
+      <c r="G79" s="1">
+        <v>30</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L79" s="1">
+        <v>35</v>
+      </c>
+      <c r="M79">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" s="4">
+        <v>46308</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D80">
+        <v>10</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F80" s="3">
+        <v>7.743055555555556E-3</v>
+      </c>
+      <c r="G80" s="1">
+        <v>0</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L80" s="1">
+        <v>35</v>
+      </c>
+      <c r="M80">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81" s="4">
+        <v>46308</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D81">
+        <v>10</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F81" s="3">
+        <v>4.9652777777777777E-3</v>
+      </c>
+      <c r="G81" s="1">
+        <v>0</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L81" s="1">
+        <v>35</v>
+      </c>
+      <c r="M81">
+        <v>530</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Helldivers/Super Credits Log.xlsx
+++ b/Helldivers/Super Credits Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\python_projects\Helldivers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{857714E1-56B5-45C4-ADDF-78DC541366EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC4928B-53F1-467F-BFA2-4CAA17DE1513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{3980E34F-3276-48B4-AAA9-72DB210AB7A4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="72">
   <si>
     <t>Mission Time</t>
   </si>
@@ -248,10 +248,13 @@
     <t>Received Supercredits from Warbond</t>
   </si>
   <si>
-    <t>Fauriant</t>
-  </si>
-  <si>
     <t>Incorrect time, had too much fun</t>
+  </si>
+  <si>
+    <t>Fronteria</t>
+  </si>
+  <si>
+    <t>Menkent</t>
   </si>
 </sst>
 </file>
@@ -653,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B874BC27-9F05-4CCB-84C0-24A63EA21ED1}">
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -4085,7 +4088,7 @@
         <v>20</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>19</v>
@@ -4229,7 +4232,171 @@
         <v>530</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82" s="4">
+        <v>46309</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D82">
+        <v>10</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F82" s="3">
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="G82" s="1">
+        <v>10</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L82" s="1">
+        <v>36</v>
+      </c>
+      <c r="M82">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83" s="4">
+        <v>46309</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D83">
+        <v>10</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F83" s="3">
+        <v>4.7337962962962967E-3</v>
+      </c>
+      <c r="G83" s="1">
+        <v>0</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L83" s="1">
+        <v>36</v>
+      </c>
+      <c r="M83">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A84" s="4">
+        <v>46309</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D84">
+        <v>10</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F84" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G84" s="1">
+        <v>0</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L84" s="1">
+        <v>36</v>
+      </c>
+      <c r="M84">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A85" s="4">
+        <v>46309</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D85">
+        <v>7</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F85" s="3">
+        <v>2.1469907407407406E-2</v>
+      </c>
+      <c r="G85" s="1">
+        <v>10</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L85" s="1">
+        <v>36</v>
+      </c>
+      <c r="M85">
+        <v>550</v>
       </c>
     </row>
   </sheetData>

--- a/Helldivers/Super Credits Log.xlsx
+++ b/Helldivers/Super Credits Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\python_projects\Helldivers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC4928B-53F1-467F-BFA2-4CAA17DE1513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E08ACD-1A74-405C-9944-27A6494ECAC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{3980E34F-3276-48B4-AAA9-72DB210AB7A4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="72">
   <si>
     <t>Mission Time</t>
   </si>
@@ -761,9 +761,7 @@
       <c r="M2" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N2" s="1"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
@@ -981,9 +979,7 @@
       <c r="M7" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N7" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -1025,9 +1021,7 @@
       <c r="M8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -1069,9 +1063,7 @@
       <c r="M9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N9" s="1"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -1113,9 +1105,7 @@
       <c r="M10" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -1157,9 +1147,7 @@
       <c r="M11" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -1201,9 +1189,7 @@
       <c r="M12" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N12" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -1245,9 +1231,7 @@
       <c r="M13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N13" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -1289,9 +1273,7 @@
       <c r="M14" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N14" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -1333,9 +1315,7 @@
       <c r="M15" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -1377,9 +1357,7 @@
       <c r="M16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N16" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N16" s="1"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
@@ -1421,9 +1399,7 @@
       <c r="M17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N17" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N17" s="1"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -1465,9 +1441,7 @@
       <c r="M18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N18" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N18" s="1"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
@@ -1509,9 +1483,7 @@
       <c r="M19" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N19" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
@@ -1641,9 +1613,7 @@
       <c r="M22" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N22" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N22" s="1"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
@@ -1773,9 +1743,7 @@
       <c r="M25">
         <v>440</v>
       </c>
-      <c r="N25" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N25" s="1"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
@@ -1817,9 +1785,7 @@
       <c r="M26">
         <v>440</v>
       </c>
-      <c r="N26" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N26" s="1"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
@@ -1861,9 +1827,7 @@
       <c r="M27">
         <v>440</v>
       </c>
-      <c r="N27" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N27" s="1"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
@@ -1905,9 +1869,7 @@
       <c r="M28">
         <v>450</v>
       </c>
-      <c r="N28" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N28" s="1"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
@@ -1949,9 +1911,7 @@
       <c r="M29">
         <v>480</v>
       </c>
-      <c r="N29" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N29" s="1"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
@@ -1993,9 +1953,7 @@
       <c r="M30">
         <v>480</v>
       </c>
-      <c r="N30" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N30" s="1"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
@@ -2037,9 +1995,7 @@
       <c r="M31">
         <v>480</v>
       </c>
-      <c r="N31" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
@@ -2081,9 +2037,7 @@
       <c r="M32">
         <v>480</v>
       </c>
-      <c r="N32" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N32" s="1"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
@@ -2125,9 +2079,7 @@
       <c r="M33">
         <v>480</v>
       </c>
-      <c r="N33" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N33" s="1"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
@@ -2169,9 +2121,7 @@
       <c r="M34">
         <v>480</v>
       </c>
-      <c r="N34" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N34" s="1"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
@@ -2213,9 +2163,7 @@
       <c r="M35">
         <v>480</v>
       </c>
-      <c r="N35" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N35" s="1"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
@@ -2257,9 +2205,7 @@
       <c r="M36">
         <v>480</v>
       </c>
-      <c r="N36" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N36" s="1"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
@@ -2301,9 +2247,7 @@
       <c r="M37">
         <v>500</v>
       </c>
-      <c r="N37" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N37" s="1"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
@@ -2345,9 +2289,7 @@
       <c r="M38">
         <v>510</v>
       </c>
-      <c r="N38" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N38" s="1"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
@@ -2433,9 +2375,7 @@
       <c r="M40">
         <v>520</v>
       </c>
-      <c r="N40" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N40" s="1"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
@@ -2565,9 +2505,7 @@
       <c r="M43">
         <v>540</v>
       </c>
-      <c r="N43" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N43" s="1"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
@@ -2609,9 +2547,7 @@
       <c r="M44">
         <v>540</v>
       </c>
-      <c r="N44" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N44" s="1"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
@@ -2697,9 +2633,7 @@
       <c r="M46">
         <v>570</v>
       </c>
-      <c r="N46" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N46" s="1"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
@@ -2829,9 +2763,7 @@
       <c r="M49">
         <v>570</v>
       </c>
-      <c r="N49" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N49" s="1"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
@@ -2917,9 +2849,7 @@
       <c r="M51">
         <v>570</v>
       </c>
-      <c r="N51" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="N51" s="1"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
@@ -3049,9 +2979,7 @@
       <c r="M54">
         <v>570</v>
       </c>
-      <c r="N54" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N54" s="1"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
@@ -3093,9 +3021,7 @@
       <c r="M55">
         <v>580</v>
       </c>
-      <c r="N55" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N55" s="1"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
@@ -3137,9 +3063,7 @@
       <c r="M56">
         <v>620</v>
       </c>
-      <c r="N56" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N56" s="1"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
@@ -3225,9 +3149,7 @@
       <c r="M58">
         <v>630</v>
       </c>
-      <c r="N58" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N58" s="1"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
@@ -3445,9 +3367,7 @@
       <c r="M63">
         <v>240</v>
       </c>
-      <c r="N63" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N63" s="1"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
@@ -3489,9 +3409,7 @@
       <c r="M64">
         <v>240</v>
       </c>
-      <c r="N64" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N64" s="1"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
@@ -3533,9 +3451,7 @@
       <c r="M65">
         <v>240</v>
       </c>
-      <c r="N65" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N65" s="1"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
@@ -3577,9 +3493,7 @@
       <c r="M66">
         <v>240</v>
       </c>
-      <c r="N66" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N66" s="1"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
@@ -3621,9 +3535,7 @@
       <c r="M67">
         <v>240</v>
       </c>
-      <c r="N67" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N67" s="1"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
@@ -3665,9 +3577,7 @@
       <c r="M68">
         <v>240</v>
       </c>
-      <c r="N68" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N68" s="1"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
@@ -3709,9 +3619,7 @@
       <c r="M69">
         <v>240</v>
       </c>
-      <c r="N69" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N69" s="1"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
@@ -3753,9 +3661,7 @@
       <c r="M70">
         <v>240</v>
       </c>
-      <c r="N70" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N70" s="1"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
@@ -3797,9 +3703,7 @@
       <c r="M71">
         <v>240</v>
       </c>
-      <c r="N71" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N71" s="1"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
@@ -3841,9 +3745,7 @@
       <c r="M72">
         <v>240</v>
       </c>
-      <c r="N72" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N72" s="1"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
@@ -3929,9 +3831,7 @@
       <c r="M74">
         <v>260</v>
       </c>
-      <c r="N74" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="N74" s="1"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="4">

--- a/Helldivers/Super Credits Log.xlsx
+++ b/Helldivers/Super Credits Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\python_projects\Helldivers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E08ACD-1A74-405C-9944-27A6494ECAC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BB4A41-F9D8-47DD-92C0-01E5D4241643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{3980E34F-3276-48B4-AAA9-72DB210AB7A4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="76">
   <si>
     <t>Mission Time</t>
   </si>
@@ -255,6 +255,18 @@
   </si>
   <si>
     <t>Menkent</t>
+  </si>
+  <si>
+    <t>Illuminates</t>
+  </si>
+  <si>
+    <t>Evacuate Priority Citizens</t>
+  </si>
+  <si>
+    <t>Retrieve Recon Craft Intel</t>
+  </si>
+  <si>
+    <t>Luxuriant</t>
   </si>
 </sst>
 </file>
@@ -656,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B874BC27-9F05-4CCB-84C0-24A63EA21ED1}">
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O1048576"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -4161,7 +4173,7 @@
         <v>71</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J82" s="1" t="s">
         <v>19</v>
@@ -4202,7 +4214,7 @@
         <v>71</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J83" s="1" t="s">
         <v>19</v>
@@ -4243,7 +4255,7 @@
         <v>71</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J84" s="1" t="s">
         <v>19</v>
@@ -4278,13 +4290,13 @@
         <v>2.1469907407407406E-2</v>
       </c>
       <c r="G85" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>71</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J85" s="1" t="s">
         <v>19</v>
@@ -4293,11 +4305,350 @@
         <v>19</v>
       </c>
       <c r="L85" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M85">
-        <v>550</v>
-      </c>
+        <v>680</v>
+      </c>
+      <c r="N85" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A86" s="4">
+        <v>46310</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D86">
+        <v>7</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F86" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L86" s="1">
+        <v>37</v>
+      </c>
+      <c r="M86">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A87" s="4">
+        <v>46310</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D87">
+        <v>10</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F87" s="3">
+        <v>1.3321759259259259E-2</v>
+      </c>
+      <c r="G87" s="1">
+        <v>0</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L87" s="1">
+        <v>38</v>
+      </c>
+      <c r="M87">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A88" s="4">
+        <v>46310</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D88">
+        <v>10</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F88" s="3">
+        <v>1.8298611111111113E-2</v>
+      </c>
+      <c r="G88" s="1">
+        <v>10</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L88" s="1">
+        <v>38</v>
+      </c>
+      <c r="M88">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A89" s="4">
+        <v>46310</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D89">
+        <v>10</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F89" s="3">
+        <v>1.556712962962963E-2</v>
+      </c>
+      <c r="G89" s="1">
+        <v>40</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L89" s="1">
+        <v>38</v>
+      </c>
+      <c r="M89">
+        <v>730</v>
+      </c>
+      <c r="N89" s="1"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A90" s="4">
+        <v>46311</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D90">
+        <v>7</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F90" s="3">
+        <v>2.6516203703703705E-2</v>
+      </c>
+      <c r="G90" s="1">
+        <v>0</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L90" s="1">
+        <v>37</v>
+      </c>
+      <c r="M90">
+        <v>730</v>
+      </c>
+      <c r="N90" s="1"/>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A91" s="4">
+        <v>46311</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D91">
+        <v>10</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F91" s="3">
+        <v>4.0277777777777777E-3</v>
+      </c>
+      <c r="G91" s="1">
+        <v>0</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L91" s="1">
+        <v>39</v>
+      </c>
+      <c r="M91">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A92" s="4">
+        <v>46311</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D92">
+        <v>10</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F92" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G92" s="1">
+        <v>10</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L92" s="1">
+        <v>39</v>
+      </c>
+      <c r="M92">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A93" s="4">
+        <v>46311</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D93">
+        <v>10</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F93" s="3">
+        <v>2.4560185185185185E-2</v>
+      </c>
+      <c r="G93" s="1">
+        <v>20</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L93" s="1">
+        <v>39</v>
+      </c>
+      <c r="M93">
+        <v>760</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="1048576" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C1048576" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Helldivers/Super Credits Log.xlsx
+++ b/Helldivers/Super Credits Log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\python_projects\Helldivers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BB4A41-F9D8-47DD-92C0-01E5D4241643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722DDCC9-E32D-4FF0-B4C7-1CDEC7F6529A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{3980E34F-3276-48B4-AAA9-72DB210AB7A4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="82">
   <si>
     <t>Mission Time</t>
   </si>
@@ -267,6 +267,24 @@
   </si>
   <si>
     <t>Luxuriant</t>
+  </si>
+  <si>
+    <t>Incorrect time, Super Credits bought, Warbond Bought</t>
+  </si>
+  <si>
+    <t>Sabotage Ammo Supplies</t>
+  </si>
+  <si>
+    <t>Fury</t>
+  </si>
+  <si>
+    <t>Get batteries 40m mission</t>
+  </si>
+  <si>
+    <t>Retrieve vaulbale personell</t>
+  </si>
+  <si>
+    <t>Zea</t>
   </si>
 </sst>
 </file>
@@ -4647,6 +4665,389 @@
         <v>42</v>
       </c>
     </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A94" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D94">
+        <v>10</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F94" s="3">
+        <v>1.5532407407407408E-2</v>
+      </c>
+      <c r="G94" s="1">
+        <v>0</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L94" s="1">
+        <v>40</v>
+      </c>
+      <c r="M94">
+        <v>860</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A95" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D95">
+        <v>10</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F95" s="3">
+        <v>2.0520833333333332E-2</v>
+      </c>
+      <c r="G95" s="1">
+        <v>10</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L95" s="1">
+        <v>40</v>
+      </c>
+      <c r="M95">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A96" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D96">
+        <v>10</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F96" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G96" s="1">
+        <v>0</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L96" s="1">
+        <v>40</v>
+      </c>
+      <c r="M96">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D97">
+        <v>10</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F97" s="3">
+        <v>1.5277777777777777E-2</v>
+      </c>
+      <c r="G97" s="1">
+        <f>M97-M96</f>
+        <v>50</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L97" s="1">
+        <v>41</v>
+      </c>
+      <c r="M97">
+        <v>920</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D98">
+        <v>10</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F98" s="3">
+        <v>2.6655092592592591E-2</v>
+      </c>
+      <c r="G98" s="1">
+        <v>10</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L98" s="1">
+        <v>42</v>
+      </c>
+      <c r="M98">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D99">
+        <v>10</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F99" s="3">
+        <v>2.9976851851851853E-3</v>
+      </c>
+      <c r="G99" s="1">
+        <f>M99-M98</f>
+        <v>0</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L99" s="1">
+        <v>42</v>
+      </c>
+      <c r="M99">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A100" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D100">
+        <v>10</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F100" s="3">
+        <v>2.0092592592592592E-2</v>
+      </c>
+      <c r="G100" s="1">
+        <f>M100-M99</f>
+        <v>0</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L100" s="1">
+        <v>42</v>
+      </c>
+      <c r="M100">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A101" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D101">
+        <v>10</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F101" s="3">
+        <v>1.6585648148148148E-2</v>
+      </c>
+      <c r="G101" s="1">
+        <f>M101-M100</f>
+        <v>0</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L101" s="1">
+        <v>43</v>
+      </c>
+      <c r="M101">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D102">
+        <v>10</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F102" s="3">
+        <v>1.8912037037037036E-2</v>
+      </c>
+      <c r="G102" s="1">
+        <f>M102-M101</f>
+        <v>0</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L102" s="1">
+        <v>44</v>
+      </c>
+      <c r="M102">
+        <v>930</v>
+      </c>
+      <c r="N102" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
     <row r="1048576" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C1048576" s="1"/>
     </row>

--- a/Helldivers/Super Credits Log.xlsx
+++ b/Helldivers/Super Credits Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\python_projects\Helldivers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722DDCC9-E32D-4FF0-B4C7-1CDEC7F6529A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64EE9C37-9919-4362-BE40-80B2BA91F1E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{3980E34F-3276-48B4-AAA9-72DB210AB7A4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="88">
   <si>
     <t>Mission Time</t>
   </si>
@@ -285,6 +285,24 @@
   </si>
   <si>
     <t>Zea</t>
+  </si>
+  <si>
+    <t>A mission</t>
+  </si>
+  <si>
+    <t>Acquire soil scan data</t>
+  </si>
+  <si>
+    <t>Incorrect mission type, Incorrect time</t>
+  </si>
+  <si>
+    <t>One big bundle</t>
+  </si>
+  <si>
+    <t>Esker</t>
+  </si>
+  <si>
+    <t>Grab valuable data ssd thing</t>
   </si>
 </sst>
 </file>
@@ -5048,6 +5066,349 @@
         <v>36</v>
       </c>
     </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A103" s="4">
+        <v>46315</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D103">
+        <v>10</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F103" s="3">
+        <v>1.8912037037037036E-2</v>
+      </c>
+      <c r="G103" s="1">
+        <f>M103-M102</f>
+        <v>0</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L103" s="1">
+        <v>44</v>
+      </c>
+      <c r="M103">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A104" s="4">
+        <v>46316</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D104">
+        <v>5</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F104" s="3">
+        <v>1.8912037037037036E-2</v>
+      </c>
+      <c r="G104" s="1">
+        <v>30</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L104" s="1">
+        <v>45</v>
+      </c>
+      <c r="M104">
+        <v>960</v>
+      </c>
+      <c r="N104" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A105" s="4">
+        <v>46316</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D105">
+        <v>5</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F105" s="3">
+        <v>2.7777777777777776E-2</v>
+      </c>
+      <c r="G105" s="1">
+        <v>30</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L105" s="1">
+        <v>45</v>
+      </c>
+      <c r="M105">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106" s="4">
+        <v>46318</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D106">
+        <v>10</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F106" s="3">
+        <v>1.8298611111111113E-2</v>
+      </c>
+      <c r="G106" s="1">
+        <v>110</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L106" s="1">
+        <v>46</v>
+      </c>
+      <c r="M106">
+        <v>1100</v>
+      </c>
+      <c r="N106" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107" s="4">
+        <v>46318</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D107">
+        <v>10</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F107" s="3">
+        <v>3.9351851851851848E-3</v>
+      </c>
+      <c r="G107" s="1">
+        <v>0</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L107" s="1">
+        <v>46</v>
+      </c>
+      <c r="M107">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108" s="4">
+        <v>46318</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D108">
+        <v>10</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F108" s="3">
+        <v>1.8715277777777779E-2</v>
+      </c>
+      <c r="G108" s="1">
+        <v>10</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L108" s="1">
+        <v>46</v>
+      </c>
+      <c r="M108">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A109" s="4">
+        <v>46318</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D109">
+        <v>10</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F109" s="3">
+        <v>1.5104166666666667E-2</v>
+      </c>
+      <c r="G109" s="1">
+        <v>30</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L109" s="1">
+        <v>46</v>
+      </c>
+      <c r="M109">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A110" s="4">
+        <v>46318</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D110">
+        <v>10</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F110" s="3">
+        <v>8.3333333333333332E-3</v>
+      </c>
+      <c r="G110" s="1">
+        <v>20</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L110" s="1">
+        <v>46</v>
+      </c>
+      <c r="M110">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="M111">
+        <v>1360</v>
+      </c>
+      <c r="N111" t="s">
+        <v>68</v>
+      </c>
+    </row>
     <row r="1048576" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C1048576" s="1"/>
     </row>
